--- a/tests/fixtures/users_v2.xlsx
+++ b/tests/fixtures/users_v2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1104,7 +1104,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>571110000006.5</v>
+        <v>571110000006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1206,6 +1206,11 @@
         <is>
           <t>Chile</t>
         </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/users_v2.xlsx
+++ b/tests/fixtures/users_v2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,6 +584,46 @@
       <c r="AE3" t="inlineStr">
         <is>
           <t>Migrated From v1</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>City Location</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Destination_other</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Prev_country_other</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Re-engagement Sent At</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Survey Completed</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Survey Sent</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>origin_country</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>transit</t>
         </is>
       </c>
     </row>
